--- a/data/trans_orig/P5701-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5701-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2007</t>
+          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>355518</t>
+          <t>351835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>417160</t>
+          <t>417082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>407487</t>
+          <t>408324</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>475713</t>
+          <t>476577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>786715</t>
+          <t>785169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>876425</t>
+          <t>877733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245896</t>
+          <t>247182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303876</t>
+          <t>302273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>347877</t>
+          <t>351453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>413516</t>
+          <t>415224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>615814</t>
+          <t>614322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>703504</t>
+          <t>696766</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>236298</t>
+          <t>235034</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>292154</t>
+          <t>290413</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>299501</t>
+          <t>298278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>362712</t>
+          <t>360231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>549697</t>
+          <t>549353</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>634465</t>
+          <t>635287</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71011</t>
+          <t>72672</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108121</t>
+          <t>109199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125176</t>
+          <t>125895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170619</t>
+          <t>172471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205224</t>
+          <t>202770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>263479</t>
+          <t>262820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>32559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,39 +1200,39 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16503</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9352</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27014</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>16503</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9373</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>26786</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26478</t>
+          <t>25145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52340</t>
+          <t>50897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>786597</t>
+          <t>784741</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>867730</t>
+          <t>867414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>687527</t>
+          <t>688622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>764575</t>
+          <t>768066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1495027</t>
+          <t>1492790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1610241</t>
+          <t>1608344</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,02%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>426506</t>
+          <t>428746</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499760</t>
+          <t>503565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,82 +1543,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>456989</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>421699</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>494610</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>26,56%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>920080</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>866535</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>968132</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>28,04%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>26,41%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>29,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>456989</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>421319</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>493582</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>31,09%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>920080</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>874841</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>978730</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>28,04%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>26,66%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285962</t>
+          <t>283044</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>348913</t>
+          <t>347882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>223008</t>
+          <t>222042</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>281974</t>
+          <t>279053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>525801</t>
+          <t>527294</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>612168</t>
+          <t>618597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47660</t>
+          <t>47080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82154</t>
+          <t>81186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90352</t>
+          <t>90519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132832</t>
+          <t>133321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150450</t>
+          <t>151839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204571</t>
+          <t>207210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36903</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27382</t>
+          <t>27257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57218</t>
+          <t>56128</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49291</t>
+          <t>47361</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85476</t>
+          <t>81976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>240163</t>
+          <t>237255</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>287257</t>
+          <t>285478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>217421</t>
+          <t>218150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>263487</t>
+          <t>262421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>473497</t>
+          <t>469446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>537753</t>
+          <t>537308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150367</t>
+          <t>151577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194172</t>
+          <t>197342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105877</t>
+          <t>106693</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144409</t>
+          <t>145057</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267004</t>
+          <t>266414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>326576</t>
+          <t>327916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>67446</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102900</t>
+          <t>102893</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56019</t>
+          <t>56587</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88618</t>
+          <t>89129</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134867</t>
+          <t>132117</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>179010</t>
+          <t>179945</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37308</t>
+          <t>36254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45705</t>
+          <t>44699</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>44473</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73970</t>
+          <t>74952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24552</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1423836</t>
+          <t>1417007</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1536681</t>
+          <t>1529384</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1355072</t>
+          <t>1360209</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1468240</t>
+          <t>1469151</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2796749</t>
+          <t>2806532</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2958658</t>
+          <t>2964400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>854500</t>
+          <t>863741</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>960230</t>
+          <t>966032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,82 +2907,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>964005</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>916465</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1018528</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>27,12%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1874147</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1803166</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1951025</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>28,16%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>29,31%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>964005</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>914117</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1020487</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>28,53%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>30,2%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1874147</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1800298</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1953065</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>619831</t>
+          <t>618861</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>707230</t>
+          <t>707187</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>604703</t>
+          <t>605616</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>696795</t>
+          <t>694996</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1248415</t>
+          <t>1246598</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1383194</t>
+          <t>1378754</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>154388</t>
+          <t>153540</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>207066</t>
+          <t>207773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>258626</t>
+          <t>258619</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>323117</t>
+          <t>323875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>425355</t>
+          <t>423859</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>516570</t>
+          <t>507131</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>71163</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46213</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>81212</t>
+          <t>81273</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91593</t>
+          <t>92518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139295</t>
+          <t>140720</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2012</t>
+          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>454971</t>
+          <t>455912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>518196</t>
+          <t>521298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>614005</t>
+          <t>617551</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>688751</t>
+          <t>692286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1096472</t>
+          <t>1089371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1194286</t>
+          <t>1188828</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>206492</t>
+          <t>203433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264313</t>
+          <t>255709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>310665</t>
+          <t>307024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>373296</t>
+          <t>371508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>530710</t>
+          <t>526585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>614978</t>
+          <t>612831</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148806</t>
+          <t>147795</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>198210</t>
+          <t>197940</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>197668</t>
+          <t>197915</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>253446</t>
+          <t>250785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>354375</t>
+          <t>360638</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>431157</t>
+          <t>434977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>47335</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78930</t>
+          <t>79278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80617</t>
+          <t>80451</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118565</t>
+          <t>121624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134852</t>
+          <t>135966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184696</t>
+          <t>187249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>10903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29482</t>
+          <t>31497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31224</t>
+          <t>32258</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,47 +4194,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>39343</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>28271</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>54074</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>2,34%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>39343</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>28031</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>55574</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1073291</t>
+          <t>1074619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1163372</t>
+          <t>1160860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>879442</t>
+          <t>882928</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>973243</t>
+          <t>971943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1979902</t>
+          <t>1981059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2110281</t>
+          <t>2108291</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444190</t>
+          <t>444089</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521068</t>
+          <t>524089</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>429990</t>
+          <t>432441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>507522</t>
+          <t>511827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>898881</t>
+          <t>901655</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1008953</t>
+          <t>1006606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>230224</t>
+          <t>229168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>291996</t>
+          <t>291556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>195580</t>
+          <t>194509</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>254836</t>
+          <t>251709</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>436169</t>
+          <t>440269</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>524308</t>
+          <t>523636</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66278</t>
+          <t>68564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107686</t>
+          <t>107578</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90083</t>
+          <t>90959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135405</t>
+          <t>136983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167779</t>
+          <t>169772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226165</t>
+          <t>227229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23695</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39059</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28775</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55987</t>
+          <t>55310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>254380</t>
+          <t>255139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>300773</t>
+          <t>302411</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>263332</t>
+          <t>263759</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>307611</t>
+          <t>307769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>533735</t>
+          <t>531967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>595690</t>
+          <t>597273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93049</t>
+          <t>91414</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131242</t>
+          <t>132465</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95376</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135240</t>
+          <t>136090</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>199979</t>
+          <t>200812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>254905</t>
+          <t>256244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48325</t>
+          <t>47732</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79491</t>
+          <t>79853</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46635</t>
+          <t>45352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77139</t>
+          <t>76983</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>115670</t>
+          <t>116250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34349</t>
+          <t>35726</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34218</t>
+          <t>33598</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>32092</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59929</t>
+          <t>59683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1817444</t>
+          <t>1819180</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1940882</t>
+          <t>1937421</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1804771</t>
+          <t>1808007</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1924970</t>
+          <t>1930385</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3668317</t>
+          <t>3659686</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3838744</t>
+          <t>3833549</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>774175</t>
+          <t>773085</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>879849</t>
+          <t>880289</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>872765</t>
+          <t>873059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>982816</t>
+          <t>980499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1673394</t>
+          <t>1670175</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1831653</t>
+          <t>1817653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>453264</t>
+          <t>454725</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>535647</t>
+          <t>541002</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>433364</t>
+          <t>434249</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>516672</t>
+          <t>523876</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>908601</t>
+          <t>915233</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1028270</t>
+          <t>1033913</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144156</t>
+          <t>144006</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>199164</t>
+          <t>197069</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>197369</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>261099</t>
+          <t>263944</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>357881</t>
+          <t>360211</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>439249</t>
+          <t>441224</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26475</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38087</t>
+          <t>37722</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69147</t>
+          <t>69017</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70140</t>
+          <t>72064</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>109402</t>
+          <t>110578</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2016</t>
+          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>275391</t>
+          <t>272304</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>324690</t>
+          <t>325869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>297511</t>
+          <t>298056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>360007</t>
+          <t>360002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>583921</t>
+          <t>588054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>666294</t>
+          <t>667778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238760</t>
+          <t>240074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290889</t>
+          <t>291310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>353473</t>
+          <t>353489</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417038</t>
+          <t>418153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>606350</t>
+          <t>605607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>687518</t>
+          <t>690684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121668</t>
+          <t>121149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163710</t>
+          <t>165397</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164076</t>
+          <t>167432</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>215881</t>
+          <t>219394</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>300659</t>
+          <t>297047</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>368996</t>
+          <t>366815</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>31756</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55587</t>
+          <t>55929</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57523</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95693</t>
+          <t>96771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98106</t>
+          <t>96510</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143929</t>
+          <t>141789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12152</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,47 +7118,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16003</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9572</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>26749</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>1,61%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>16003</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9245</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>26412</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32511</t>
+          <t>31757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>828408</t>
+          <t>834841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>925755</t>
+          <t>924619</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>788003</t>
+          <t>787283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>877372</t>
+          <t>874941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1647631</t>
+          <t>1647168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1770978</t>
+          <t>1773083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>734151</t>
+          <t>736849</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>826660</t>
+          <t>826647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>745672</t>
+          <t>750800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>833862</t>
+          <t>839329</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505328</t>
+          <t>1515387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1632995</t>
+          <t>1639079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>271018</t>
+          <t>270777</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>336108</t>
+          <t>335923</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>244896</t>
+          <t>244822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>307568</t>
+          <t>304570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>531251</t>
+          <t>533176</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>622102</t>
+          <t>626558</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72642</t>
+          <t>74152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112921</t>
+          <t>113029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61269</t>
+          <t>62164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96774</t>
+          <t>97338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143354</t>
+          <t>144392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198177</t>
+          <t>198672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28660</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18264</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42967</t>
+          <t>42965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>242624</t>
+          <t>241572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290556</t>
+          <t>289716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>246656</t>
+          <t>249900</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>295935</t>
+          <t>295762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>506095</t>
+          <t>505332</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>573231</t>
+          <t>573414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171654</t>
+          <t>172740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217885</t>
+          <t>218403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162885</t>
+          <t>160031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203621</t>
+          <t>203951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346045</t>
+          <t>344889</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409532</t>
+          <t>408225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49967</t>
+          <t>50071</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81424</t>
+          <t>82339</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49283</t>
+          <t>49678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81482</t>
+          <t>79180</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106640</t>
+          <t>106635</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>152711</t>
+          <t>154670</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>29007</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40585</t>
+          <t>39606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59754</t>
+          <t>59240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1389352</t>
+          <t>1388161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1505011</t>
+          <t>1503834</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1365802</t>
+          <t>1372045</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1489105</t>
+          <t>1484359</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2792067</t>
+          <t>2783339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2955793</t>
+          <t>2950781</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1183469</t>
+          <t>1182897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1297011</t>
+          <t>1296622</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1298475</t>
+          <t>1302910</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1418045</t>
+          <t>1416240</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2516393</t>
+          <t>2521600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2682939</t>
+          <t>2683779</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>465239</t>
+          <t>466276</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>553253</t>
+          <t>553122</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>490905</t>
+          <t>492530</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>578357</t>
+          <t>576954</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>976237</t>
+          <t>984185</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1097927</t>
+          <t>1106391</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130259</t>
+          <t>129138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178253</t>
+          <t>179315</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>155537</t>
+          <t>154405</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>210632</t>
+          <t>210601</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>294948</t>
+          <t>293743</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>370811</t>
+          <t>372026</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39039</t>
+          <t>39302</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43071</t>
+          <t>42947</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42234</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>75028</t>
+          <t>73870</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2023</t>
+          <t>Población según la frecuencia de recibir visitas de amigos y familiares en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>207152</t>
+          <t>208442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>247616</t>
+          <t>249440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>281262</t>
+          <t>280734</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>321618</t>
+          <t>321528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>499533</t>
+          <t>500892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>559250</t>
+          <t>560775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130246</t>
+          <t>130549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>170219</t>
+          <t>168439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224993</t>
+          <t>223326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261916</t>
+          <t>260301</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>365258</t>
+          <t>364747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>420674</t>
+          <t>419073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62957</t>
+          <t>63469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92533</t>
+          <t>92903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>95180</t>
+          <t>94527</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122790</t>
+          <t>123992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>164607</t>
+          <t>165974</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>206822</t>
+          <t>207917</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33486</t>
+          <t>34165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55960</t>
+          <t>54869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>58574</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81151</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97587</t>
+          <t>98470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129177</t>
+          <t>131499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24889</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49801</t>
+          <t>46344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68324</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1228263</t>
+          <t>1224738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1635823</t>
+          <t>1649107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>785963</t>
+          <t>765785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1220281</t>
+          <t>1221549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2141128</t>
+          <t>2132367</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2742460</t>
+          <t>2776916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459628</t>
+          <t>471148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>774985</t>
+          <t>774254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501065</t>
+          <t>486479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773694</t>
+          <t>770843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1086397</t>
+          <t>1097581</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1502476</t>
+          <t>1500028</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106211</t>
+          <t>98497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186922</t>
+          <t>187819</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>161506</t>
+          <t>158272</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>892369</t>
+          <t>873821</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>307693</t>
+          <t>302891</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1143131</t>
+          <t>1156041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59211</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106855</t>
+          <t>107272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68582</t>
+          <t>67258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115557</t>
+          <t>115011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140969</t>
+          <t>143105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213162</t>
+          <t>214050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>29334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>18669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43642</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65512</t>
+          <t>66102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>354464</t>
+          <t>353424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>408586</t>
+          <t>409226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>376666</t>
+          <t>376949</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>422069</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>746005</t>
+          <t>746091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>816149</t>
+          <t>818676</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156364</t>
+          <t>158101</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204124</t>
+          <t>204214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157454</t>
+          <t>156814</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195303</t>
+          <t>195842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324894</t>
+          <t>322347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>385952</t>
+          <t>383343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>34635</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82209</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33413</t>
+          <t>32930</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58059</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73374</t>
+          <t>74058</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>123726</t>
+          <t>124949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39366</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24904</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43471</t>
+          <t>41941</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45947</t>
+          <t>46463</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75415</t>
+          <t>76001</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1828778</t>
+          <t>1834593</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2280590</t>
+          <t>2315251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1448921</t>
+          <t>1448125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1922952</t>
+          <t>1929768</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3440822</t>
+          <t>3455015</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4091642</t>
+          <t>4088934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>780878</t>
+          <t>758301</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1101829</t>
+          <t>1097777</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>886651</t>
+          <t>908555</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1187263</t>
+          <t>1187337</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1820896</t>
+          <t>1793259</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2241536</t>
+          <t>2244721</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>218416</t>
+          <t>215641</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>323933</t>
+          <t>329335</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>317217</t>
+          <t>313346</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1098882</t>
+          <t>1111977</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>585148</t>
+          <t>586269</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1362408</t>
+          <t>1481892</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120113</t>
+          <t>117982</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>180121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>161382</t>
+          <t>159225</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225004</t>
+          <t>223072</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>303983</t>
+          <t>300928</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>394158</t>
+          <t>387037</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60841</t>
+          <t>60744</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50324</t>
+          <t>50876</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90682</t>
+          <t>91757</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90907</t>
+          <t>92261</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139136</t>
+          <t>137088</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5701-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5701-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>351835</t>
+          <t>356134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>417082</t>
+          <t>420031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>408324</t>
+          <t>406982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>476577</t>
+          <t>471285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>785169</t>
+          <t>775945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>877733</t>
+          <t>870605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>247182</t>
+          <t>243954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>302273</t>
+          <t>300205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>351453</t>
+          <t>351425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>415224</t>
+          <t>417647</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>614322</t>
+          <t>615837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>696766</t>
+          <t>700759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>235034</t>
+          <t>235098</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>290413</t>
+          <t>288722</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>298278</t>
+          <t>297980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>360231</t>
+          <t>361932</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>549353</t>
+          <t>552264</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>635287</t>
+          <t>631627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72672</t>
+          <t>71754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109199</t>
+          <t>107830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125895</t>
+          <t>122555</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172471</t>
+          <t>169205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>202770</t>
+          <t>205405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>262820</t>
+          <t>263134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32559</t>
+          <t>32663</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27014</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25145</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50897</t>
+          <t>53246</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>784741</t>
+          <t>785030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>867414</t>
+          <t>867384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>688622</t>
+          <t>685074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>768066</t>
+          <t>768273</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1492790</t>
+          <t>1496520</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1608344</t>
+          <t>1612851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>428746</t>
+          <t>426684</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503565</t>
+          <t>501573</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>421699</t>
+          <t>421104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>494610</t>
+          <t>492277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>866535</t>
+          <t>872036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>968132</t>
+          <t>975554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283044</t>
+          <t>284187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>347882</t>
+          <t>346357</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222042</t>
+          <t>224434</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>279053</t>
+          <t>283555</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>527294</t>
+          <t>525949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>618597</t>
+          <t>612609</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47080</t>
+          <t>48187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81186</t>
+          <t>81797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90519</t>
+          <t>89534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133321</t>
+          <t>131376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151839</t>
+          <t>149382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207210</t>
+          <t>204107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>57048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47361</t>
+          <t>48269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81976</t>
+          <t>84961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>237255</t>
+          <t>237039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>285478</t>
+          <t>287490</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>218150</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>262421</t>
+          <t>266526</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>469446</t>
+          <t>473414</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>537308</t>
+          <t>537121</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151577</t>
+          <t>152346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197342</t>
+          <t>197513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106693</t>
+          <t>104296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145057</t>
+          <t>144602</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>266414</t>
+          <t>267417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>327916</t>
+          <t>325370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67446</t>
+          <t>69083</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102893</t>
+          <t>104922</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56587</t>
+          <t>57680</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89129</t>
+          <t>88824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>132117</t>
+          <t>136380</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>179945</t>
+          <t>183259</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>44910</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44473</t>
+          <t>42950</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74952</t>
+          <t>73158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>15292</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1417007</t>
+          <t>1417219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1529384</t>
+          <t>1534599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1360209</t>
+          <t>1353109</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1469151</t>
+          <t>1465672</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2806532</t>
+          <t>2807715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2964400</t>
+          <t>2969898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>863741</t>
+          <t>861563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>966032</t>
+          <t>964107</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>916465</t>
+          <t>913745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1018528</t>
+          <t>1013524</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1803166</t>
+          <t>1797277</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1951025</t>
+          <t>1949224</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>618861</t>
+          <t>617061</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>707187</t>
+          <t>712513</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>605616</t>
+          <t>609001</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>694996</t>
+          <t>695785</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1246598</t>
+          <t>1253632</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1378754</t>
+          <t>1383604</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153540</t>
+          <t>153083</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>207773</t>
+          <t>207041</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>258619</t>
+          <t>256415</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>323875</t>
+          <t>322552</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>423859</t>
+          <t>425397</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>507131</t>
+          <t>508141</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69529</t>
+          <t>70072</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>48309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>82365</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92518</t>
+          <t>94852</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>140720</t>
+          <t>139936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>455912</t>
+          <t>455601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>521298</t>
+          <t>520211</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>617551</t>
+          <t>618432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>692286</t>
+          <t>693211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1089371</t>
+          <t>1090194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1188828</t>
+          <t>1187898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203433</t>
+          <t>204875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255709</t>
+          <t>260658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307024</t>
+          <t>309378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>371508</t>
+          <t>373333</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526585</t>
+          <t>532501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>612831</t>
+          <t>617615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>147307</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>197940</t>
+          <t>196583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>197915</t>
+          <t>193134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>250785</t>
+          <t>253334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>360638</t>
+          <t>357761</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>434977</t>
+          <t>441453</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47335</t>
+          <t>45635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79278</t>
+          <t>77556</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80451</t>
+          <t>78056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121624</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135966</t>
+          <t>133190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187249</t>
+          <t>186324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31497</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>55177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1074619</t>
+          <t>1068719</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1160860</t>
+          <t>1160272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>882928</t>
+          <t>886023</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>971943</t>
+          <t>972301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1981059</t>
+          <t>1980929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2108291</t>
+          <t>2102798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,58%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444089</t>
+          <t>443953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524089</t>
+          <t>523376</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>432441</t>
+          <t>435334</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511827</t>
+          <t>508656</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>901655</t>
+          <t>897582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1006606</t>
+          <t>1007588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>229168</t>
+          <t>228465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>291556</t>
+          <t>296155</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194509</t>
+          <t>195319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251709</t>
+          <t>253388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>440269</t>
+          <t>444099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>523636</t>
+          <t>530262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68564</t>
+          <t>68882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107578</t>
+          <t>109170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90959</t>
+          <t>88240</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136983</t>
+          <t>132012</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169772</t>
+          <t>167167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227229</t>
+          <t>228640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>23855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41036</t>
+          <t>40144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>28506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55310</t>
+          <t>56651</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>255139</t>
+          <t>255074</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>302411</t>
+          <t>301602</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>263759</t>
+          <t>263935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>307769</t>
+          <t>307046</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>531967</t>
+          <t>528738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>597273</t>
+          <t>595112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91414</t>
+          <t>94373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132465</t>
+          <t>131405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95843</t>
+          <t>95464</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136090</t>
+          <t>134133</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>200812</t>
+          <t>200551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>256244</t>
+          <t>256210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47732</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79853</t>
+          <t>79927</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>21892</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45352</t>
+          <t>46805</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76983</t>
+          <t>77824</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116250</t>
+          <t>117152</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35726</t>
+          <t>34098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>31002</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59683</t>
+          <t>59640</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17901</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1819180</t>
+          <t>1828598</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1937421</t>
+          <t>1944089</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1808007</t>
+          <t>1801557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1930385</t>
+          <t>1934553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3659686</t>
+          <t>3662566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3833549</t>
+          <t>3832420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>773085</t>
+          <t>775947</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>880289</t>
+          <t>873785</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>873059</t>
+          <t>871144</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>980499</t>
+          <t>977854</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1670175</t>
+          <t>1675793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1817653</t>
+          <t>1826629</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>454725</t>
+          <t>455069</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>541002</t>
+          <t>539001</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>434249</t>
+          <t>436395</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>523876</t>
+          <t>518098</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>915233</t>
+          <t>908539</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1033913</t>
+          <t>1027776</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144006</t>
+          <t>142599</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>197069</t>
+          <t>198802</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>200425</t>
+          <t>200390</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>263944</t>
+          <t>262826</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>360211</t>
+          <t>362725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>441224</t>
+          <t>446983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25873</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52462</t>
+          <t>51660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37722</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69017</t>
+          <t>68241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>72064</t>
+          <t>70161</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>110578</t>
+          <t>110564</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>272304</t>
+          <t>272368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>325869</t>
+          <t>325911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>298056</t>
+          <t>298560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>360002</t>
+          <t>360853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>588054</t>
+          <t>582752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>667778</t>
+          <t>664817</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240074</t>
+          <t>239641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291310</t>
+          <t>290765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>353489</t>
+          <t>354108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>418153</t>
+          <t>414854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>605607</t>
+          <t>609417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690684</t>
+          <t>688232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121149</t>
+          <t>122402</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165397</t>
+          <t>163507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167432</t>
+          <t>167799</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>219394</t>
+          <t>220134</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>297047</t>
+          <t>298662</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>366815</t>
+          <t>369802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31756</t>
+          <t>32164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>57116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59735</t>
+          <t>59667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96771</t>
+          <t>100169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96510</t>
+          <t>97289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141789</t>
+          <t>144984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>26303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31757</t>
+          <t>33052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>834841</t>
+          <t>834376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>924619</t>
+          <t>928139</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>787283</t>
+          <t>787950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>874941</t>
+          <t>874204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1647168</t>
+          <t>1643063</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1773083</t>
+          <t>1771064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>736849</t>
+          <t>734281</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>826647</t>
+          <t>824180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>750800</t>
+          <t>749063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>839329</t>
+          <t>838401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1515387</t>
+          <t>1510472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1639079</t>
+          <t>1637311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>270777</t>
+          <t>270199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>335923</t>
+          <t>334910</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>244822</t>
+          <t>244732</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>304570</t>
+          <t>305570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>533176</t>
+          <t>534019</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>626558</t>
+          <t>624459</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74152</t>
+          <t>73399</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113029</t>
+          <t>112897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62164</t>
+          <t>60868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97338</t>
+          <t>98193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144392</t>
+          <t>144278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198672</t>
+          <t>195546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29246</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>19978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42965</t>
+          <t>43040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>241572</t>
+          <t>241262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>289716</t>
+          <t>290434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>249900</t>
+          <t>248580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>295762</t>
+          <t>295237</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>505332</t>
+          <t>502057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>573414</t>
+          <t>573541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,42%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172740</t>
+          <t>171375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>218403</t>
+          <t>217711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160031</t>
+          <t>159984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203951</t>
+          <t>205600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>344889</t>
+          <t>344768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408225</t>
+          <t>408001</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50071</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82339</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49678</t>
+          <t>48851</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79180</t>
+          <t>78286</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106635</t>
+          <t>107065</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>154670</t>
+          <t>153091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29007</t>
+          <t>27623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39606</t>
+          <t>41502</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59240</t>
+          <t>60948</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1388161</t>
+          <t>1385604</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1503834</t>
+          <t>1501968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1372045</t>
+          <t>1371426</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1484359</t>
+          <t>1489194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2783339</t>
+          <t>2786805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2950781</t>
+          <t>2954630</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,83%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1182897</t>
+          <t>1186811</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1296622</t>
+          <t>1295626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1302910</t>
+          <t>1299034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1416240</t>
+          <t>1418343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2521600</t>
+          <t>2519874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2683779</t>
+          <t>2688141</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>466276</t>
+          <t>467861</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>553122</t>
+          <t>551146</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>492530</t>
+          <t>488696</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>576954</t>
+          <t>574259</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>984185</t>
+          <t>981496</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1106391</t>
+          <t>1098907</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129138</t>
+          <t>129557</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179315</t>
+          <t>178560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154405</t>
+          <t>154617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>210601</t>
+          <t>213528</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>293743</t>
+          <t>298329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>372026</t>
+          <t>370927</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39302</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>20174</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42947</t>
+          <t>44586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42412</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>73179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>227891</t>
+          <t>253176</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>208442</t>
+          <t>231874</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249440</t>
+          <t>276736</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>301331</t>
+          <t>320596</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>280734</t>
+          <t>301312</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>321528</t>
+          <t>345153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>529222</t>
+          <t>573772</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>500892</t>
+          <t>544191</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>560775</t>
+          <t>605946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>148732</t>
+          <t>158780</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130549</t>
+          <t>138150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168439</t>
+          <t>180595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>243365</t>
+          <t>269841</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>223326</t>
+          <t>250029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260301</t>
+          <t>292061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>392097</t>
+          <t>428621</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>364747</t>
+          <t>399622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>419073</t>
+          <t>456367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77113</t>
+          <t>94492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63469</t>
+          <t>74587</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92903</t>
+          <t>114632</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>108905</t>
+          <t>120215</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94527</t>
+          <t>105258</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123992</t>
+          <t>136390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>186019</t>
+          <t>214706</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>165974</t>
+          <t>190852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>207917</t>
+          <t>237856</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43123</t>
+          <t>52079</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34165</t>
+          <t>40646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54869</t>
+          <t>65753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69487</t>
+          <t>79986</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58574</t>
+          <t>66242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81783</t>
+          <t>92698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>112610</t>
+          <t>132065</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98470</t>
+          <t>115581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131499</t>
+          <t>151611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -10057,102 +10057,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26232</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>27776</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20447</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>37145</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>46964</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>36591</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>58183</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>29216</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>20402</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>46344</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>46496</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>35579</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>66547</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514139</t>
+          <t>577716</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514139</t>
+          <t>577716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514139</t>
+          <t>577716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>752304</t>
+          <t>818413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>752304</t>
+          <t>818413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>752304</t>
+          <t>818413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1266443</t>
+          <t>1396128</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1266443</t>
+          <t>1396128</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1266443</t>
+          <t>1396128</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1357571</t>
+          <t>1179598</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1224738</t>
+          <t>1124973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1649107</t>
+          <t>1233894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1079599</t>
+          <t>1075052</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>765785</t>
+          <t>1030916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1221549</t>
+          <t>1121080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2437169</t>
+          <t>2254649</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2132367</t>
+          <t>2189559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2776916</t>
+          <t>2328502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>673967</t>
+          <t>742879</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471148</t>
+          <t>696038</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>774254</t>
+          <t>793634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>675257</t>
+          <t>761193</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>486479</t>
+          <t>723064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770843</t>
+          <t>806393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1349223</t>
+          <t>1504073</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1097581</t>
+          <t>1438812</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1500028</t>
+          <t>1567140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>153741</t>
+          <t>169813</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98497</t>
+          <t>145379</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>187819</t>
+          <t>199826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>358870</t>
+          <t>175975</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158272</t>
+          <t>154899</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>873821</t>
+          <t>200523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>512612</t>
+          <t>345788</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>302891</t>
+          <t>311897</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1156041</t>
+          <t>386160</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85551</t>
+          <t>111258</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107272</t>
+          <t>134904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94320</t>
+          <t>118729</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67258</t>
+          <t>98614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115011</t>
+          <t>140474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>179871</t>
+          <t>229986</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143105</t>
+          <t>203020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214050</t>
+          <t>264814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19335</t>
+          <t>25149</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29334</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>39876</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>29191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>54612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>48547</t>
+          <t>65025</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>50581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66102</t>
+          <t>84015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2290165</t>
+          <t>2228697</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2290165</t>
+          <t>2228697</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2290165</t>
+          <t>2228697</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2237258</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2237258</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2237258</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4527422</t>
+          <t>4399521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4527422</t>
+          <t>4399521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4527422</t>
+          <t>4399521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>383033</t>
+          <t>420744</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>353424</t>
+          <t>392794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>409226</t>
+          <t>447947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>399482</t>
+          <t>435131</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>376949</t>
+          <t>412936</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>422069</t>
+          <t>459398</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>782515</t>
+          <t>855875</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>746091</t>
+          <t>816835</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>818676</t>
+          <t>891913</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>179137</t>
+          <t>198529</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158101</t>
+          <t>175313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204214</t>
+          <t>226364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>175781</t>
+          <t>198062</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156814</t>
+          <t>177828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195842</t>
+          <t>220603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>354918</t>
+          <t>396590</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>322347</t>
+          <t>366234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383343</t>
+          <t>432472</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49317</t>
+          <t>48685</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>35057</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80014</t>
+          <t>63411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>50233</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32930</t>
+          <t>38564</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>93256</t>
+          <t>98918</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74058</t>
+          <t>82810</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124949</t>
+          <t>118847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>31037</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41125</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32729</t>
+          <t>40341</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24081</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41941</t>
+          <t>52237</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>58985</t>
+          <t>71378</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46463</t>
+          <t>58180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76001</t>
+          <t>89987</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20575</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>18018</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>733902</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>733902</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>733902</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445489</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445489</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1306927</t>
+          <t>1445489</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1968494</t>
+          <t>1853518</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1834593</t>
+          <t>1786724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2315251</t>
+          <t>1922448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1780412</t>
+          <t>1830778</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1448125</t>
+          <t>1780457</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1929768</t>
+          <t>1891668</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3748906</t>
+          <t>3684296</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3455015</t>
+          <t>3594967</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4088934</t>
+          <t>3766586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1001836</t>
+          <t>1100188</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>758301</t>
+          <t>1040621</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1097777</t>
+          <t>1158124</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1094402</t>
+          <t>1229095</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>908555</t>
+          <t>1174681</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1187337</t>
+          <t>1277931</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2096238</t>
+          <t>2329283</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1793259</t>
+          <t>2254883</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2244721</t>
+          <t>2416286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>280172</t>
+          <t>312990</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>215641</t>
+          <t>279706</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>329335</t>
+          <t>352599</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>511714</t>
+          <t>346422</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>313346</t>
+          <t>314512</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1111977</t>
+          <t>377156</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>791886</t>
+          <t>659412</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>586269</t>
+          <t>609743</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1481892</t>
+          <t>718009</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>154930</t>
+          <t>194374</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117982</t>
+          <t>168327</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180121</t>
+          <t>224429</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>196536</t>
+          <t>239055</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>159225</t>
+          <t>212863</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>223072</t>
+          <t>266068</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>351466</t>
+          <t>433429</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>300928</t>
+          <t>396802</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>387037</t>
+          <t>475749</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>45495</t>
+          <t>56930</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>42307</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60744</t>
+          <t>75421</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>66801</t>
+          <t>77788</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50876</t>
+          <t>62406</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91757</t>
+          <t>97336</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>112297</t>
+          <t>134717</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92261</t>
+          <t>114399</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137088</t>
+          <t>157987</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3450927</t>
+          <t>3518000</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3450927</t>
+          <t>3518000</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3450927</t>
+          <t>3518000</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3649865</t>
+          <t>3723138</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3649865</t>
+          <t>3723138</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3649865</t>
+          <t>3723138</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7100792</t>
+          <t>7241138</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7100792</t>
+          <t>7241138</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7100792</t>
+          <t>7241138</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
